--- a/database/13-R_T_hh_eff.xlsx
+++ b/database/13-R_T_hh_eff.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\2024-IDESIGNRES\_BACKUPS_\Herramienta\Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\D\2024-IDESIGNRES\git\buildings\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{821474B4-1E1F-4402-AD5C-D49C3034061A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76BD3AB-7F31-43E2-8831-9B1A8A6764F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EF11B127-9037-40AB-BF2E-2FFA21B0772B}"/>
   </bookViews>
@@ -110,7 +110,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="107">
   <si>
     <t>AT</t>
   </si>
@@ -277,9 +277,6 @@
     <t>Hydrogen</t>
   </si>
   <si>
-    <t>_Electricity in circulation</t>
-  </si>
-  <si>
     <t>Electricity in circulation</t>
   </si>
   <si>
@@ -428,6 +425,12 @@
   </si>
   <si>
     <t>Water heating_Advanced electric heating</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>Space heating_Electricity in circulation</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1024,7 @@
   <sheetPr codeName="Hoja9">
     <tabColor theme="8" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:AO43"/>
+  <dimension ref="A1:AP43"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="41.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1029,19 +1032,19 @@
     <col min="3" max="3" width="10.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" customWidth="1"/>
     <col min="5" max="7" width="10" customWidth="1"/>
-    <col min="8" max="41" width="7.85546875" customWidth="1"/>
-    <col min="42" max="75" width="13.28515625" customWidth="1"/>
+    <col min="8" max="42" width="7.85546875" customWidth="1"/>
+    <col min="43" max="76" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -1053,7 +1056,7 @@
         <v>2</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>3</v>
@@ -1092,13 +1095,13 @@
         <v>15</v>
       </c>
       <c r="T1" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="U1" s="2" t="s">
         <v>16</v>
       </c>
       <c r="V1" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="W1" s="2" t="s">
         <v>17</v>
@@ -1110,10 +1113,10 @@
         <v>19</v>
       </c>
       <c r="Z1" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="AA1" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="AB1" s="2" t="s">
         <v>20</v>
@@ -1122,7 +1125,7 @@
         <v>21</v>
       </c>
       <c r="AD1" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AE1" s="2" t="s">
         <v>22</v>
@@ -1134,7 +1137,7 @@
         <v>24</v>
       </c>
       <c r="AH1" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="AI1" s="2" t="s">
         <v>25</v>
@@ -1146,21 +1149,24 @@
         <v>27</v>
       </c>
       <c r="AL1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="AO1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="AN1" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>28</v>
@@ -1282,8 +1288,11 @@
       <c r="AO2" s="4">
         <v>0.81221545500821446</v>
       </c>
+      <c r="AP2" s="4">
+        <v>0.81221545500821446</v>
+      </c>
     </row>
-    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -1407,8 +1416,11 @@
       <c r="AO3" s="6">
         <v>0.69733063004848161</v>
       </c>
+      <c r="AP3" s="6">
+        <v>0.69733063004848161</v>
+      </c>
     </row>
-    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>31</v>
       </c>
@@ -1532,8 +1544,11 @@
       <c r="AO4" s="6">
         <v>0.68864242495836636</v>
       </c>
+      <c r="AP4" s="6">
+        <v>0.68864242495836636</v>
+      </c>
     </row>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -1657,8 +1672,11 @@
       <c r="AO5" s="6">
         <v>0.66140466000033404</v>
       </c>
+      <c r="AP5" s="6">
+        <v>0.66140466000033404</v>
+      </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -1782,8 +1800,11 @@
       <c r="AO6" s="6">
         <v>2.8343196992672799</v>
       </c>
+      <c r="AP6" s="6">
+        <v>2.8343196992672799</v>
+      </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -1907,8 +1928,11 @@
       <c r="AO7" s="6">
         <v>0.75867987915520152</v>
       </c>
+      <c r="AP7" s="6">
+        <v>0.75867987915520152</v>
+      </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -2032,8 +2056,11 @@
       <c r="AO8" s="6">
         <v>0.72004022236969445</v>
       </c>
+      <c r="AP8" s="6">
+        <v>0.72004022236969445</v>
+      </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -2157,8 +2184,11 @@
       <c r="AO9" s="6">
         <v>0.86868388504864391</v>
       </c>
+      <c r="AP9" s="6">
+        <v>0.86868388504864391</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -2198,9 +2228,7 @@
       <c r="M10" s="6">
         <v>0.75155680373604472</v>
       </c>
-      <c r="N10" s="6">
-        <v>0</v>
-      </c>
+      <c r="N10" s="6"/>
       <c r="O10" s="6">
         <v>0.90469334930793488</v>
       </c>
@@ -2282,8 +2310,11 @@
       <c r="AO10" s="6">
         <v>0.83833006429072365</v>
       </c>
+      <c r="AP10" s="6">
+        <v>0.83833006429072365</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -2405,8 +2436,11 @@
       <c r="AO11" s="6">
         <v>3.1954581103752822</v>
       </c>
+      <c r="AP11" s="6">
+        <v>3.1954581103752822</v>
+      </c>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>47</v>
       </c>
@@ -2530,8 +2564,11 @@
       <c r="AO12" s="7">
         <v>0.83023787900921497</v>
       </c>
+      <c r="AP12" s="7">
+        <v>0.83023787900921497</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -2655,8 +2692,11 @@
       <c r="AO13" s="8">
         <v>0</v>
       </c>
+      <c r="AP13" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>51</v>
       </c>
@@ -2780,8 +2820,11 @@
       <c r="AO14" s="8">
         <v>0</v>
       </c>
+      <c r="AP14" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>53</v>
       </c>
@@ -2905,138 +2948,144 @@
       <c r="AO15" s="8">
         <v>0</v>
       </c>
+      <c r="AP15" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="10">
+        <v>1</v>
+      </c>
+      <c r="D16" s="10">
+        <v>1</v>
+      </c>
+      <c r="E16" s="10">
+        <v>1</v>
+      </c>
+      <c r="F16" s="10">
+        <v>1</v>
+      </c>
+      <c r="G16" s="10">
+        <v>1</v>
+      </c>
+      <c r="H16" s="10">
+        <v>1</v>
+      </c>
+      <c r="I16" s="10">
+        <v>1</v>
+      </c>
+      <c r="J16" s="10">
+        <v>1</v>
+      </c>
+      <c r="K16" s="10">
+        <v>1</v>
+      </c>
+      <c r="L16" s="10">
+        <v>1</v>
+      </c>
+      <c r="M16" s="10">
+        <v>1</v>
+      </c>
+      <c r="N16" s="10">
+        <v>1</v>
+      </c>
+      <c r="O16" s="10">
+        <v>1</v>
+      </c>
+      <c r="P16" s="10">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="10">
+        <v>1</v>
+      </c>
+      <c r="R16" s="10">
+        <v>1</v>
+      </c>
+      <c r="S16" s="10">
+        <v>1</v>
+      </c>
+      <c r="T16" s="10">
+        <v>1</v>
+      </c>
+      <c r="U16" s="10">
+        <v>1</v>
+      </c>
+      <c r="V16" s="10">
+        <v>1</v>
+      </c>
+      <c r="W16" s="10">
+        <v>1</v>
+      </c>
+      <c r="X16" s="10">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="10">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AI16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AJ16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AL16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AM16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AN16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO16" s="10">
+        <v>1</v>
+      </c>
+      <c r="AP16" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="10">
-        <v>1</v>
-      </c>
-      <c r="D16" s="10">
-        <v>1</v>
-      </c>
-      <c r="E16" s="10">
-        <v>1</v>
-      </c>
-      <c r="F16" s="10">
-        <v>1</v>
-      </c>
-      <c r="G16" s="10">
-        <v>1</v>
-      </c>
-      <c r="H16" s="10">
-        <v>1</v>
-      </c>
-      <c r="I16" s="10">
-        <v>1</v>
-      </c>
-      <c r="J16" s="10">
-        <v>1</v>
-      </c>
-      <c r="K16" s="10">
-        <v>1</v>
-      </c>
-      <c r="L16" s="10">
-        <v>1</v>
-      </c>
-      <c r="M16" s="10">
-        <v>1</v>
-      </c>
-      <c r="N16" s="10">
-        <v>1</v>
-      </c>
-      <c r="O16" s="10">
-        <v>1</v>
-      </c>
-      <c r="P16" s="10">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="10">
-        <v>1</v>
-      </c>
-      <c r="R16" s="10">
-        <v>1</v>
-      </c>
-      <c r="S16" s="10">
-        <v>1</v>
-      </c>
-      <c r="T16" s="10">
-        <v>1</v>
-      </c>
-      <c r="U16" s="10">
-        <v>1</v>
-      </c>
-      <c r="V16" s="10">
-        <v>1</v>
-      </c>
-      <c r="W16" s="10">
-        <v>1</v>
-      </c>
-      <c r="X16" s="10">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="10">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AD16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AE16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AF16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AH16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AI16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AJ16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AK16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AL16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AM16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AN16" s="10">
-        <v>1</v>
-      </c>
-      <c r="AO16" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="B17" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>58</v>
       </c>
       <c r="C17" s="4">
         <v>3.8863101121769841</v>
@@ -3155,10 +3204,13 @@
       <c r="AO17" s="4">
         <v>3.8863101121769841</v>
       </c>
+      <c r="AP17" s="4">
+        <v>3.8863101121769841</v>
+      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>36</v>
@@ -3272,13 +3324,16 @@
       <c r="AO18" s="6">
         <v>1.485077256325535</v>
       </c>
+      <c r="AP18" s="6">
+        <v>1.485077256325535</v>
+      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>61</v>
       </c>
       <c r="C19" s="6">
         <v>3.8863101121769841</v>
@@ -3397,13 +3452,16 @@
       <c r="AO19" s="6">
         <v>3.8863101121769841</v>
       </c>
+      <c r="AP19" s="6">
+        <v>3.8863101121769841</v>
+      </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="C20" s="4">
         <v>0.79742339305388443</v>
@@ -3522,10 +3580,13 @@
       <c r="AO20" s="4">
         <v>0.79742339305388443</v>
       </c>
+      <c r="AP20" s="4">
+        <v>0.79742339305388443</v>
+      </c>
     </row>
-    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>30</v>
@@ -3647,10 +3708,13 @@
       <c r="AO21" s="6">
         <v>0.74676821339675747</v>
       </c>
+      <c r="AP21" s="6">
+        <v>0.74676821339675747</v>
+      </c>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>32</v>
@@ -3772,10 +3836,13 @@
       <c r="AO22" s="6">
         <v>0.77538652673708952</v>
       </c>
+      <c r="AP22" s="6">
+        <v>0.77538652673708952</v>
+      </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>34</v>
@@ -3897,10 +3964,13 @@
       <c r="AO23" s="6">
         <v>0.71526272073948405</v>
       </c>
+      <c r="AP23" s="6">
+        <v>0.71526272073948405</v>
+      </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>38</v>
@@ -4022,10 +4092,13 @@
       <c r="AO24" s="6">
         <v>0.78150973703344762</v>
       </c>
+      <c r="AP24" s="6">
+        <v>0.78150973703344762</v>
+      </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>40</v>
@@ -4147,10 +4220,13 @@
       <c r="AO25" s="6">
         <v>0.79909748517448953</v>
       </c>
+      <c r="AP25" s="6">
+        <v>0.79909748517448953</v>
+      </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>42</v>
@@ -4272,10 +4348,13 @@
       <c r="AO26" s="6">
         <v>0.89021879219676769</v>
       </c>
+      <c r="AP26" s="6">
+        <v>0.89021879219676769</v>
+      </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>44</v>
@@ -4313,9 +4392,7 @@
       <c r="M27" s="6">
         <v>0.83564430624173758</v>
       </c>
-      <c r="N27" s="6">
-        <v>0</v>
-      </c>
+      <c r="N27" s="6"/>
       <c r="O27" s="6">
         <v>0.92075771359873804</v>
       </c>
@@ -4397,10 +4474,13 @@
       <c r="AO27" s="6">
         <v>0.87558669928322341</v>
       </c>
+      <c r="AP27" s="6">
+        <v>0.87558669928322341</v>
+      </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>46</v>
@@ -4522,13 +4602,16 @@
       <c r="AO28" s="6">
         <v>3.1954581103752822</v>
       </c>
+      <c r="AP28" s="6">
+        <v>3.1954581103752822</v>
+      </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="5" t="s">
         <v>71</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>72</v>
       </c>
       <c r="C29" s="7">
         <v>0.76805471009501414</v>
@@ -4647,10 +4730,13 @@
       <c r="AO29" s="7">
         <v>0.76805471009501414</v>
       </c>
+      <c r="AP29" s="7">
+        <v>0.76805471009501414</v>
+      </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>50</v>
@@ -4772,10 +4858,13 @@
       <c r="AO30" s="8">
         <v>0</v>
       </c>
+      <c r="AP30" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>52</v>
@@ -4897,10 +4986,13 @@
       <c r="AO31" s="8">
         <v>0</v>
       </c>
+      <c r="AP31" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>54</v>
@@ -5022,13 +5114,16 @@
       <c r="AO32" s="8">
         <v>0</v>
       </c>
+      <c r="AP32" s="8">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>75</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="C33" s="10">
         <v>1.0000000000001401</v>
@@ -5147,13 +5242,16 @@
       <c r="AO33" s="10">
         <v>1.0000000000001401</v>
       </c>
+      <c r="AP33" s="10">
+        <v>1.0000000000001401</v>
+      </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>79</v>
       </c>
       <c r="C34" s="4">
         <v>0.73199043638043859</v>
@@ -5272,10 +5370,13 @@
       <c r="AO34" s="4">
         <v>0.73199043638043859</v>
       </c>
+      <c r="AP34" s="4">
+        <v>0.73199043638043859</v>
+      </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>30</v>
@@ -5397,10 +5498,13 @@
       <c r="AO35" s="6">
         <v>0.59145670230925207</v>
       </c>
+      <c r="AP35" s="6">
+        <v>0.59145670230925207</v>
+      </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>32</v>
@@ -5522,10 +5626,13 @@
       <c r="AO36" s="6">
         <v>0.60805417652680993</v>
       </c>
+      <c r="AP36" s="6">
+        <v>0.60805417652680993</v>
+      </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>38</v>
@@ -5647,10 +5754,13 @@
       <c r="AO37" s="6">
         <v>0.61534633038198139</v>
       </c>
+      <c r="AP37" s="6">
+        <v>0.61534633038198139</v>
+      </c>
     </row>
-    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>40</v>
@@ -5772,13 +5882,16 @@
       <c r="AO38" s="6">
         <v>0.58081073226119251</v>
       </c>
+      <c r="AP38" s="6">
+        <v>0.58081073226119251</v>
+      </c>
     </row>
-    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C39" s="12">
         <v>0.84464946645586403</v>
@@ -5897,388 +6010,400 @@
       <c r="AO39" s="12">
         <v>0.84464946645586403</v>
       </c>
+      <c r="AP39" s="12">
+        <v>0.84464946645586403</v>
+      </c>
     </row>
-    <row r="40" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>84</v>
+      </c>
+      <c r="B40" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="C40" s="7">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7">
+        <v>1</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1</v>
+      </c>
+      <c r="F40" s="7">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7">
+        <v>1</v>
+      </c>
+      <c r="H40" s="7">
+        <v>1</v>
+      </c>
+      <c r="I40" s="7">
+        <v>1</v>
+      </c>
+      <c r="J40" s="7">
+        <v>1</v>
+      </c>
+      <c r="K40" s="7">
+        <v>1</v>
+      </c>
+      <c r="L40" s="7">
+        <v>1</v>
+      </c>
+      <c r="M40" s="7">
+        <v>1</v>
+      </c>
+      <c r="N40" s="7">
+        <v>1</v>
+      </c>
+      <c r="O40" s="7">
+        <v>1</v>
+      </c>
+      <c r="P40" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="7">
+        <v>1</v>
+      </c>
+      <c r="R40" s="7">
+        <v>1</v>
+      </c>
+      <c r="S40" s="7">
+        <v>1</v>
+      </c>
+      <c r="T40" s="7">
+        <v>1</v>
+      </c>
+      <c r="U40" s="7">
+        <v>1</v>
+      </c>
+      <c r="V40" s="7">
+        <v>1</v>
+      </c>
+      <c r="W40" s="7">
+        <v>1</v>
+      </c>
+      <c r="X40" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y40" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AM40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO40" s="7">
+        <v>1</v>
+      </c>
+      <c r="AP40" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>86</v>
       </c>
-      <c r="C40" s="7">
-        <v>1</v>
-      </c>
-      <c r="D40" s="7">
-        <v>1</v>
-      </c>
-      <c r="E40" s="7">
-        <v>1</v>
-      </c>
-      <c r="F40" s="7">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7">
-        <v>1</v>
-      </c>
-      <c r="H40" s="7">
-        <v>1</v>
-      </c>
-      <c r="I40" s="7">
-        <v>1</v>
-      </c>
-      <c r="J40" s="7">
-        <v>1</v>
-      </c>
-      <c r="K40" s="7">
-        <v>1</v>
-      </c>
-      <c r="L40" s="7">
-        <v>1</v>
-      </c>
-      <c r="M40" s="7">
-        <v>1</v>
-      </c>
-      <c r="N40" s="7">
-        <v>1</v>
-      </c>
-      <c r="O40" s="7">
-        <v>1</v>
-      </c>
-      <c r="P40" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q40" s="7">
-        <v>1</v>
-      </c>
-      <c r="R40" s="7">
-        <v>1</v>
-      </c>
-      <c r="S40" s="7">
-        <v>1</v>
-      </c>
-      <c r="T40" s="7">
-        <v>1</v>
-      </c>
-      <c r="U40" s="7">
-        <v>1</v>
-      </c>
-      <c r="V40" s="7">
-        <v>1</v>
-      </c>
-      <c r="W40" s="7">
-        <v>1</v>
-      </c>
-      <c r="X40" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y40" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AD40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AF40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AG40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AK40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AL40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AM40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AN40" s="7">
-        <v>1</v>
-      </c>
-      <c r="AO40" s="7">
+      <c r="B41" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C41" s="7">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7">
+        <v>1</v>
+      </c>
+      <c r="E41" s="7">
+        <v>1</v>
+      </c>
+      <c r="F41" s="7">
+        <v>1</v>
+      </c>
+      <c r="G41" s="7">
+        <v>1</v>
+      </c>
+      <c r="H41" s="7">
+        <v>1</v>
+      </c>
+      <c r="I41" s="7">
+        <v>1</v>
+      </c>
+      <c r="J41" s="7">
+        <v>1</v>
+      </c>
+      <c r="K41" s="7">
+        <v>1</v>
+      </c>
+      <c r="L41" s="7">
+        <v>1</v>
+      </c>
+      <c r="M41" s="7">
+        <v>1</v>
+      </c>
+      <c r="N41" s="7">
+        <v>1</v>
+      </c>
+      <c r="O41" s="7">
+        <v>1</v>
+      </c>
+      <c r="P41" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="7">
+        <v>1</v>
+      </c>
+      <c r="R41" s="7">
+        <v>1</v>
+      </c>
+      <c r="S41" s="7">
+        <v>1</v>
+      </c>
+      <c r="T41" s="7">
+        <v>1</v>
+      </c>
+      <c r="U41" s="7">
+        <v>1</v>
+      </c>
+      <c r="V41" s="7">
+        <v>1</v>
+      </c>
+      <c r="W41" s="7">
+        <v>1</v>
+      </c>
+      <c r="X41" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y41" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AM41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO41" s="7">
+        <v>1</v>
+      </c>
+      <c r="AP41" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>87</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" s="7">
-        <v>1</v>
-      </c>
-      <c r="D41" s="7">
-        <v>1</v>
-      </c>
-      <c r="E41" s="7">
-        <v>1</v>
-      </c>
-      <c r="F41" s="7">
-        <v>1</v>
-      </c>
-      <c r="G41" s="7">
-        <v>1</v>
-      </c>
-      <c r="H41" s="7">
-        <v>1</v>
-      </c>
-      <c r="I41" s="7">
-        <v>1</v>
-      </c>
-      <c r="J41" s="7">
-        <v>1</v>
-      </c>
-      <c r="K41" s="7">
-        <v>1</v>
-      </c>
-      <c r="L41" s="7">
-        <v>1</v>
-      </c>
-      <c r="M41" s="7">
-        <v>1</v>
-      </c>
-      <c r="N41" s="7">
-        <v>1</v>
-      </c>
-      <c r="O41" s="7">
-        <v>1</v>
-      </c>
-      <c r="P41" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q41" s="7">
-        <v>1</v>
-      </c>
-      <c r="R41" s="7">
-        <v>1</v>
-      </c>
-      <c r="S41" s="7">
-        <v>1</v>
-      </c>
-      <c r="T41" s="7">
-        <v>1</v>
-      </c>
-      <c r="U41" s="7">
-        <v>1</v>
-      </c>
-      <c r="V41" s="7">
-        <v>1</v>
-      </c>
-      <c r="W41" s="7">
-        <v>1</v>
-      </c>
-      <c r="X41" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y41" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AD41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AF41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AG41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AK41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AL41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AM41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AN41" s="7">
-        <v>1</v>
-      </c>
-      <c r="AO41" s="7">
+      <c r="B42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="7">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7">
+        <v>1</v>
+      </c>
+      <c r="E42" s="7">
+        <v>1</v>
+      </c>
+      <c r="F42" s="7">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7">
+        <v>1</v>
+      </c>
+      <c r="H42" s="7">
+        <v>1</v>
+      </c>
+      <c r="I42" s="7">
+        <v>1</v>
+      </c>
+      <c r="J42" s="7">
+        <v>1</v>
+      </c>
+      <c r="K42" s="7">
+        <v>1</v>
+      </c>
+      <c r="L42" s="7">
+        <v>1</v>
+      </c>
+      <c r="M42" s="7">
+        <v>1</v>
+      </c>
+      <c r="N42" s="7">
+        <v>1</v>
+      </c>
+      <c r="O42" s="7">
+        <v>1</v>
+      </c>
+      <c r="P42" s="7">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="7">
+        <v>1</v>
+      </c>
+      <c r="R42" s="7">
+        <v>1</v>
+      </c>
+      <c r="S42" s="7">
+        <v>1</v>
+      </c>
+      <c r="T42" s="7">
+        <v>1</v>
+      </c>
+      <c r="U42" s="7">
+        <v>1</v>
+      </c>
+      <c r="V42" s="7">
+        <v>1</v>
+      </c>
+      <c r="W42" s="7">
+        <v>1</v>
+      </c>
+      <c r="X42" s="7">
+        <v>1</v>
+      </c>
+      <c r="Y42" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AA42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AD42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AH42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AI42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AJ42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AK42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AM42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AN42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AO42" s="7">
+        <v>1</v>
+      </c>
+      <c r="AP42" s="7">
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" s="3" t="s">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
         <v>89</v>
       </c>
-      <c r="C42" s="7">
-        <v>1</v>
-      </c>
-      <c r="D42" s="7">
-        <v>1</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1</v>
-      </c>
-      <c r="F42" s="7">
-        <v>1</v>
-      </c>
-      <c r="G42" s="7">
-        <v>1</v>
-      </c>
-      <c r="H42" s="7">
-        <v>1</v>
-      </c>
-      <c r="I42" s="7">
-        <v>1</v>
-      </c>
-      <c r="J42" s="7">
-        <v>1</v>
-      </c>
-      <c r="K42" s="7">
-        <v>1</v>
-      </c>
-      <c r="L42" s="7">
-        <v>1</v>
-      </c>
-      <c r="M42" s="7">
-        <v>1</v>
-      </c>
-      <c r="N42" s="7">
-        <v>1</v>
-      </c>
-      <c r="O42" s="7">
-        <v>1</v>
-      </c>
-      <c r="P42" s="7">
-        <v>1</v>
-      </c>
-      <c r="Q42" s="7">
-        <v>1</v>
-      </c>
-      <c r="R42" s="7">
-        <v>1</v>
-      </c>
-      <c r="S42" s="7">
-        <v>1</v>
-      </c>
-      <c r="T42" s="7">
-        <v>1</v>
-      </c>
-      <c r="U42" s="7">
-        <v>1</v>
-      </c>
-      <c r="V42" s="7">
-        <v>1</v>
-      </c>
-      <c r="W42" s="7">
-        <v>1</v>
-      </c>
-      <c r="X42" s="7">
-        <v>1</v>
-      </c>
-      <c r="Y42" s="7">
-        <v>1</v>
-      </c>
-      <c r="Z42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AA42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AB42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AC42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AD42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AE42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AF42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AG42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AH42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AI42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AJ42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AK42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AL42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AM42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AN42" s="7">
-        <v>1</v>
-      </c>
-      <c r="AO42" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>90</v>
-      </c>
       <c r="B43" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C43" s="7">
         <v>1</v>
@@ -6395,6 +6520,9 @@
         <v>1</v>
       </c>
       <c r="AO43" s="7">
+        <v>1</v>
+      </c>
+      <c r="AP43" s="7">
         <v>1</v>
       </c>
     </row>
@@ -6405,14 +6533,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d5a454ad-01f5-4994-82d1-6709f21d0815" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -6421,7 +6541,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101001152DA57635F794DA1B55AD2A1650750" ma:contentTypeVersion="18" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="d50453dcf73aba94928ea9ce699f876f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d5a454ad-01f5-4994-82d1-6709f21d0815" xmlns:ns4="f189dc43-7b2c-48c4-bff8-a83f0c0a7b6e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ed076703a2edef292be04cd44655221b" ns3:_="" ns4:_="">
     <xsd:import namespace="d5a454ad-01f5-4994-82d1-6709f21d0815"/>
@@ -6674,24 +6794,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB9DA360-41E3-4743-A15E-B56181903D09}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="d5a454ad-01f5-4994-82d1-6709f21d0815"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f189dc43-7b2c-48c4-bff8-a83f0c0a7b6e"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d5a454ad-01f5-4994-82d1-6709f21d0815" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{491C569D-494B-4D43-B80B-0800828823CF}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -6699,7 +6810,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{61D256B6-0D78-4690-A5F5-201D9C814F93}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6716,4 +6827,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB9DA360-41E3-4743-A15E-B56181903D09}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="d5a454ad-01f5-4994-82d1-6709f21d0815"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f189dc43-7b2c-48c4-bff8-a83f0c0a7b6e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>